--- a/output/pdf_financials_xlsx/AI.xlsx
+++ b/output/pdf_financials_xlsx/AI.xlsx
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
-        <v>0</v>
+        <v>1.315017</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>0</v>
+        <v>10.628383</v>
       </c>
       <c r="D46" s="3" t="n">
         <v>0</v>
@@ -3239,10 +3239,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0</v>
+        <v>1.315017</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0</v>
+        <v>10.628383</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
@@ -19965,7 +19965,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E139" s="5" t="n">

--- a/output/pdf_financials_xlsx/AI.xlsx
+++ b/output/pdf_financials_xlsx/AI.xlsx
@@ -1175,10 +1175,10 @@
         <v>1.571162</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>2.816304</v>
+        <v>2.901738</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>4.011</v>
+        <v>4.158</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>6.781</v>
@@ -7760,13 +7760,13 @@
         <v>0</v>
       </c>
       <c r="M136" s="3" t="n">
-        <v>0</v>
+        <v>-0.378</v>
       </c>
       <c r="N136" s="3" t="n">
         <v>0</v>
       </c>
       <c r="O136" s="3" t="n">
-        <v>0</v>
+        <v>-0.041</v>
       </c>
     </row>
     <row r="137">
@@ -24549,7 +24549,11 @@
           <t>Repurchase of shares 9</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -26589,7 +26593,11 @@
           <t>Repurchase of common shares</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -45287,7 +45295,11 @@
           <t>Directors’ fees 8</t>
         </is>
       </c>
-      <c r="D442" t="inlineStr"/>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E442" t="inlineStr">
         <is>
           <t>-</t>
